--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -1389,7 +1389,79 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>דירה 12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01--2026-12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>מזומן</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>19/26</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>documents/payments/2026-09-16-apartment-12-vaad-fee-1200-receipt.jpg</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Наличными; квитанция № 19/26 от 2026-09-16. Оплата за весь 2026 год: 12 × 100 ILS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:N21"/>
 </worksheet>
 </file>
--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-08-06-apartment-16-vaad-fee-1200.jpg; documents/payments/2026-08-06-apartment-16-vaad-fee-1200-receipt.jpg</t>
+          <t>documents/payments/apartment-16-vaad-fee-2026-08-06-1200.jpg; documents/payments/apartment-16-vaad-fee-2026-08-06-1200-receipt.jpg</t>
         </is>
       </c>
       <c r="N3" s="0" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-02-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-02-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N4" s="0" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-03-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-03-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N5" s="0" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-04-vaad-fee-400.jpg</t>
+          <t>documents/payments/apartment-04-vaad-fee-2026-06-04-400.jpg</t>
         </is>
       </c>
       <c r="N6" s="0" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-05-vaad-fee-500.jpg</t>
+          <t>documents/payments/apartment-05-vaad-fee-2026-06-04-500.jpg</t>
         </is>
       </c>
       <c r="N7" s="0" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-08-13-apartment-01-vaad-fee-200.jpg; documents/payments/2026-08-13-apartment-01-vaad-fee-200-receipt.jpg</t>
+          <t>documents/payments/apartment-01-vaad-fee-2026-08-13-200.jpg; documents/payments/apartment-01-vaad-fee-2026-08-13-200-receipt.jpg</t>
         </is>
       </c>
       <c r="N8" s="0" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-06-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-06-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N9" s="0" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-07-vaad-fee-1200.jpg</t>
+          <t>documents/payments/apartment-07-vaad-fee-2026-06-04-1200.jpg</t>
         </is>
       </c>
       <c r="N10" s="0" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-08-vaad-fee-500.jpg</t>
+          <t>documents/payments/apartment-08-vaad-fee-2026-06-04-500.jpg</t>
         </is>
       </c>
       <c r="N11" s="0" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-09-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-09-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N12" s="0" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-17-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-17-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N15" s="0" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-18-vaad-fee-1200.jpg</t>
+          <t>documents/payments/apartment-18-vaad-fee-2026-06-04-1200.jpg</t>
         </is>
       </c>
       <c r="N16" s="0" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-04-apartment-19-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-19-vaad-fee-2026-06-04-600.jpg</t>
         </is>
       </c>
       <c r="N17" s="0" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-06-apartment-14-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-14-vaad-fee-2026-06-06-600.jpg</t>
         </is>
       </c>
       <c r="N18" s="0" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-06-08-apartment-01-vaad-fee-600.jpg</t>
+          <t>documents/payments/apartment-01-vaad-fee-2026-06-08-600.jpg</t>
         </is>
       </c>
       <c r="N19" s="0" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-09-03-apartment-20-vaad-fee-1200.jpg</t>
+          <t>documents/payments/apartment-20-vaad-fee-2026-09-03-1200.jpg</t>
         </is>
       </c>
       <c r="N20" s="0" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-09-16-apartment-12-vaad-fee-1200-receipt.jpg</t>
+          <t>documents/payments/apartment-12-vaad-fee-2026-09-16-1200-receipt.jpg</t>
         </is>
       </c>
       <c r="N21" s="0" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-10-05-apartment-04-vaad-fee-300-receipt-21-26.jpg</t>
+          <t>documents/payments/apartment-04-vaad-fee-2026-10-05-300-receipt-21-26.jpg</t>
         </is>
       </c>
       <c r="N22" s="0" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>documents/payments/2026-10-05-apartment-04-vaad-fee-300-receipt-20-26.jpg</t>
+          <t>documents/payments/apartment-04-vaad-fee-2026-10-05-300-receipt-20-26.jpg</t>
         </is>
       </c>
       <c r="N23" s="0" t="inlineStr">

--- a/finance/payments.xlsx
+++ b/finance/payments.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -1845,8 +1845,74 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="32" customHeight="1" s="0">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>owners.xlsx / דירה 3</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>דירה 3</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>2026-07--2026-12</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>מס ועד בית</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>לא צוין בקבלה</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>22/26</t>
+        </is>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>оплачено</t>
+        </is>
+      </c>
+      <c r="M24" s="0" t="inlineStr">
+        <is>
+          <t>documents/payments/apartment-03-vaad-fee-2026-10-14-600-receipt-22-26.jpg</t>
+        </is>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>Оплата за июль--декабрь 2026: 6 × 100 ILS; квитанция № 22/26 от 2026-10-14, сумма 300 + 300 ILS. Способ оплаты не указан.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N23"/>
+  <autoFilter ref="A1:N24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>